--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,12 +429,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -430,34 +442,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22.6787608535532</v>
+        <v>27.6759764370951</v>
       </c>
       <c r="B2" t="n">
-        <v>85.9812874870685</v>
+        <v>78.80450557534293</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16.29770595792319</v>
+        <v>13.23915118553265</v>
       </c>
       <c r="B3" t="n">
-        <v>74.69841714945537</v>
+        <v>77.76356840971103</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>26.15639512632801</v>
+        <v>22.68193998447312</v>
       </c>
       <c r="B4" t="n">
-        <v>75.69994961106734</v>
+        <v>73.68908354504887</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12.22678061272482</v>
+        <v>23.77393403370445</v>
       </c>
       <c r="B5" t="n">
-        <v>79.25786968483231</v>
+        <v>85.58035691292213</v>
       </c>
     </row>
   </sheetData>

--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -442,34 +442,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>27.6759764370951</v>
+        <v>22.6787608535532</v>
       </c>
       <c r="B2" t="n">
-        <v>78.80450557534293</v>
+        <v>85.9812874870685</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>13.23915118553265</v>
+        <v>16.29770595792319</v>
       </c>
       <c r="B3" t="n">
-        <v>77.76356840971103</v>
+        <v>74.69841714945537</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22.68193998447312</v>
+        <v>26.15639512632801</v>
       </c>
       <c r="B4" t="n">
-        <v>73.68908354504887</v>
+        <v>75.69994961106734</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>23.77393403370445</v>
+        <v>12.22678061272482</v>
       </c>
       <c r="B5" t="n">
-        <v>85.58035691292213</v>
+        <v>79.25786968483231</v>
       </c>
     </row>
   </sheetData>

--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -442,34 +442,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22.6787608535532</v>
+        <v>27.6759764370951</v>
       </c>
       <c r="B2" t="n">
-        <v>85.9812874870685</v>
+        <v>78.80450557534293</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16.29770595792319</v>
+        <v>13.23915118553265</v>
       </c>
       <c r="B3" t="n">
-        <v>74.69841714945537</v>
+        <v>77.76356840971103</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>26.15639512632801</v>
+        <v>22.68193998447312</v>
       </c>
       <c r="B4" t="n">
-        <v>75.69994961106734</v>
+        <v>73.68908354504887</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12.22678061272482</v>
+        <v>23.77393403370445</v>
       </c>
       <c r="B5" t="n">
-        <v>79.25786968483231</v>
+        <v>85.58035691292213</v>
       </c>
     </row>
   </sheetData>

--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,34 +442,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22.6787608535532</v>
+        <v>15.58997052954</v>
       </c>
       <c r="B2" t="n">
-        <v>85.9812874870685</v>
+        <v>74.81079033369666</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16.29770595792319</v>
+        <v>20.69756483395233</v>
       </c>
       <c r="B3" t="n">
-        <v>74.69841714945537</v>
+        <v>83.18375473562189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>26.15639512632801</v>
+        <v>23.70053406468846</v>
       </c>
       <c r="B4" t="n">
-        <v>75.69994961106734</v>
+        <v>75.48339311090085</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12.22678061272482</v>
+        <v>12.0615823523145</v>
       </c>
       <c r="B5" t="n">
-        <v>79.25786968483231</v>
+        <v>79.21246318764263</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>26.3784266269447</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90.30073020949595</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>32.37160285248694</v>
+      </c>
+      <c r="B7" t="n">
+        <v>74.72066897280459</v>
       </c>
     </row>
   </sheetData>

--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -442,50 +442,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15.58997052954</v>
+        <v>15.464</v>
       </c>
       <c r="B2" t="n">
-        <v>74.81079033369666</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20.69756483395233</v>
+        <v>21.473</v>
       </c>
       <c r="B3" t="n">
-        <v>83.18375473562189</v>
+        <v>83.968</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23.70053406468846</v>
+        <v>23.455</v>
       </c>
       <c r="B4" t="n">
-        <v>75.48339311090085</v>
+        <v>75.425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12.0615823523145</v>
+        <v>11.932</v>
       </c>
       <c r="B5" t="n">
-        <v>79.21246318764263</v>
+        <v>79.80800000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>26.3784266269447</v>
+        <v>26.855</v>
       </c>
       <c r="B6" t="n">
-        <v>90.30073020949595</v>
+        <v>89.38200000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32.37160285248694</v>
+        <v>32.645</v>
       </c>
       <c r="B7" t="n">
-        <v>74.72066897280459</v>
+        <v>74.90300000000001</v>
       </c>
     </row>
   </sheetData>

--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,26 +442,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15.464</v>
+        <v>22.254</v>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>84.908</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>21.473</v>
+        <v>16.168</v>
       </c>
       <c r="B3" t="n">
-        <v>83.968</v>
+        <v>74.82899999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="B4" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="5">
@@ -470,22 +470,6 @@
       </c>
       <c r="B5" t="n">
         <v>79.80800000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>26.855</v>
-      </c>
-      <c r="B6" t="n">
-        <v>89.38200000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>32.645</v>
-      </c>
-      <c r="B7" t="n">
-        <v>74.90300000000001</v>
       </c>
     </row>
   </sheetData>

--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -425,51 +425,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>dc_lat</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>dc_long</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dc_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22.254</v>
+        <v>22.6787608535532</v>
       </c>
       <c r="B2" t="n">
-        <v>84.908</v>
+        <v>85.9812874870685</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16.168</v>
+        <v>16.29770595792319</v>
       </c>
       <c r="B3" t="n">
-        <v>74.82899999999999</v>
+        <v>74.69841714945537</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>26.803</v>
+        <v>26.15639512632801</v>
       </c>
       <c r="B4" t="n">
-        <v>75.81</v>
+        <v>75.69994961106734</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11.932</v>
+        <v>12.22678061272482</v>
       </c>
       <c r="B5" t="n">
-        <v>79.80800000000001</v>
+        <v>79.25786968483231</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22.6787608535532</v>
+        <v>32.44403356398158</v>
       </c>
       <c r="B2" t="n">
-        <v>85.9812874870685</v>
+        <v>74.73044569195511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16.29770595792319</v>
+        <v>12.04874799532531</v>
       </c>
       <c r="B3" t="n">
-        <v>74.69841714945537</v>
+        <v>79.21150505358439</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>26.15639512632801</v>
+        <v>23.61535700184445</v>
       </c>
       <c r="B4" t="n">
-        <v>75.69994961106734</v>
+        <v>75.75889788525319</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,14 +486,40 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12.22678061272482</v>
+        <v>15.54977075059852</v>
       </c>
       <c r="B5" t="n">
-        <v>79.25786968483231</v>
+        <v>74.78945392278645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>DC_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>26.35404548900413</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90.29082073684187</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DC_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>20.42453784629396</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83.47886457363825</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DC_6</t>
         </is>
       </c>
     </row>

--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>32.44403356398158</v>
+        <v>22.6787608535532</v>
       </c>
       <c r="B2" t="n">
-        <v>74.73044569195511</v>
+        <v>85.9812874870685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>12.04874799532531</v>
+        <v>16.29770595792319</v>
       </c>
       <c r="B3" t="n">
-        <v>79.21150505358439</v>
+        <v>74.69841714945537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23.61535700184445</v>
+        <v>26.15639512632801</v>
       </c>
       <c r="B4" t="n">
-        <v>75.75889788525319</v>
+        <v>75.69994961106734</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,40 +486,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15.54977075059852</v>
+        <v>12.22678061272482</v>
       </c>
       <c r="B5" t="n">
-        <v>74.78945392278645</v>
+        <v>79.25786968483231</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>DC_4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>26.35404548900413</v>
-      </c>
-      <c r="B6" t="n">
-        <v>90.29082073684187</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DC_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>20.42453784629396</v>
-      </c>
-      <c r="B7" t="n">
-        <v>83.47886457363825</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DC_6</t>
         </is>
       </c>
     </row>

--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>32.44403356398158</v>
+        <v>15.464</v>
       </c>
       <c r="B2" t="n">
-        <v>74.73044569195511</v>
+        <v>75</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>12.04874799532531</v>
+        <v>21.473</v>
       </c>
       <c r="B3" t="n">
-        <v>79.21150505358439</v>
+        <v>83.968</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23.61535700184445</v>
+        <v>23.455</v>
       </c>
       <c r="B4" t="n">
-        <v>75.75889788525319</v>
+        <v>75.425</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15.54977075059852</v>
+        <v>11.932</v>
       </c>
       <c r="B5" t="n">
-        <v>74.78945392278645</v>
+        <v>79.80800000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>26.35404548900413</v>
+        <v>26.855</v>
       </c>
       <c r="B6" t="n">
-        <v>90.29082073684187</v>
+        <v>89.38200000000001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20.42453784629396</v>
+        <v>32.645</v>
       </c>
       <c r="B7" t="n">
-        <v>83.47886457363825</v>
+        <v>74.90300000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/dc_locations.xlsx
+++ b/dc_locations.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15.464</v>
+        <v>11.932</v>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>79.80800000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>21.473</v>
+        <v>23.455</v>
       </c>
       <c r="B3" t="n">
-        <v>83.968</v>
+        <v>75.425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23.455</v>
+        <v>26.855</v>
       </c>
       <c r="B4" t="n">
-        <v>75.425</v>
+        <v>89.38200000000001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11.932</v>
+        <v>15.464</v>
       </c>
       <c r="B5" t="n">
-        <v>79.80800000000001</v>
+        <v>75</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>26.855</v>
+        <v>21.473</v>
       </c>
       <c r="B6" t="n">
-        <v>89.38200000000001</v>
+        <v>83.968</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
